--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6284,7 +6284,21 @@
       </c>
     </row>
     <row r="307" spans="1:5">
-      <c r="A307" s="1"/>
+      <c r="A307" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B307">
+        <v>1</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+      <c r="D307">
+        <v>1</v>
+      </c>
+      <c r="E307">
+        <v>4</v>
+      </c>
     </row>
     <row r="308" spans="1:5">
       <c r="A308" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6301,7 +6301,21 @@
       </c>
     </row>
     <row r="308" spans="1:5">
-      <c r="A308" s="1"/>
+      <c r="A308" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B308">
+        <v>19</v>
+      </c>
+      <c r="C308">
+        <v>17</v>
+      </c>
+      <c r="D308">
+        <v>16</v>
+      </c>
+      <c r="E308">
+        <v>22</v>
+      </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6318,10 +6318,38 @@
       </c>
     </row>
     <row r="309" spans="1:5">
-      <c r="A309" s="1"/>
+      <c r="A309" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B309">
+        <v>34</v>
+      </c>
+      <c r="C309">
+        <v>36</v>
+      </c>
+      <c r="D309">
+        <v>38</v>
+      </c>
+      <c r="E309">
+        <v>40</v>
+      </c>
     </row>
     <row r="310" spans="1:5">
-      <c r="A310" s="1"/>
+      <c r="A310" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B310">
+        <v>20</v>
+      </c>
+      <c r="C310">
+        <v>15</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310">
+        <v>24</v>
+      </c>
     </row>
     <row r="311" spans="1:5">
       <c r="A311" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6352,7 +6352,21 @@
       </c>
     </row>
     <row r="311" spans="1:5">
-      <c r="A311" s="1"/>
+      <c r="A311" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B311">
+        <v>29</v>
+      </c>
+      <c r="C311">
+        <v>33</v>
+      </c>
+      <c r="D311">
+        <v>42</v>
+      </c>
+      <c r="E311">
+        <v>44</v>
+      </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6369,7 +6369,21 @@
       </c>
     </row>
     <row r="312" spans="1:5">
-      <c r="A312" s="1"/>
+      <c r="A312" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B312">
+        <v>23</v>
+      </c>
+      <c r="C312">
+        <v>26</v>
+      </c>
+      <c r="D312">
+        <v>43</v>
+      </c>
+      <c r="E312">
+        <v>45</v>
+      </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6386,13 +6386,55 @@
       </c>
     </row>
     <row r="313" spans="1:5">
-      <c r="A313" s="1"/>
+      <c r="A313" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B313">
+        <v>31</v>
+      </c>
+      <c r="C313">
+        <v>19</v>
+      </c>
+      <c r="D313">
+        <v>27</v>
+      </c>
+      <c r="E313">
+        <v>26</v>
+      </c>
     </row>
     <row r="314" spans="1:5">
-      <c r="A314" s="1"/>
+      <c r="A314" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B314">
+        <v>35</v>
+      </c>
+      <c r="C314">
+        <v>31</v>
+      </c>
+      <c r="D314">
+        <v>32</v>
+      </c>
+      <c r="E314">
+        <v>37</v>
+      </c>
     </row>
     <row r="315" spans="1:5">
-      <c r="A315" s="1"/>
+      <c r="A315" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B315">
+        <v>30</v>
+      </c>
+      <c r="C315">
+        <v>20</v>
+      </c>
+      <c r="D315">
+        <v>24</v>
+      </c>
+      <c r="E315">
+        <v>28</v>
+      </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -6437,16 +6437,72 @@
       </c>
     </row>
     <row r="316" spans="1:5">
-      <c r="A316" s="1"/>
+      <c r="A316" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B316">
+        <v>30</v>
+      </c>
+      <c r="C316">
+        <v>21</v>
+      </c>
+      <c r="D316">
+        <v>29</v>
+      </c>
+      <c r="E316">
+        <v>39</v>
+      </c>
     </row>
     <row r="317" spans="1:5">
-      <c r="A317" s="1"/>
+      <c r="A317" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B317">
+        <v>74</v>
+      </c>
+      <c r="C317">
+        <v>74</v>
+      </c>
+      <c r="D317">
+        <v>74</v>
+      </c>
+      <c r="E317">
+        <v>78</v>
+      </c>
     </row>
     <row r="318" spans="1:5">
-      <c r="A318" s="1"/>
+      <c r="A318" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B318">
+        <v>59</v>
+      </c>
+      <c r="C318">
+        <v>62</v>
+      </c>
+      <c r="D318">
+        <v>63</v>
+      </c>
+      <c r="E318">
+        <v>72</v>
+      </c>
     </row>
     <row r="319" spans="1:5">
-      <c r="A319" s="1"/>
+      <c r="A319" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B319">
+        <v>70</v>
+      </c>
+      <c r="C319">
+        <v>78</v>
+      </c>
+      <c r="D319">
+        <v>78</v>
+      </c>
+      <c r="E319">
+        <v>80</v>
+      </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" s="1"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -1186,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E322"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.8181818181818"/>
@@ -6505,13 +6505,157 @@
       </c>
     </row>
     <row r="320" spans="1:5">
-      <c r="A320" s="1"/>
-    </row>
-    <row r="321" spans="1:1">
-      <c r="A321" s="1"/>
-    </row>
-    <row r="322" spans="1:1">
-      <c r="A322" s="1"/>
+      <c r="A320" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B320">
+        <v>69</v>
+      </c>
+      <c r="C320">
+        <v>80</v>
+      </c>
+      <c r="D320">
+        <v>79</v>
+      </c>
+      <c r="E320">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B321">
+        <v>81</v>
+      </c>
+      <c r="C321">
+        <v>87</v>
+      </c>
+      <c r="D321">
+        <v>92</v>
+      </c>
+      <c r="E321">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B322">
+        <v>85</v>
+      </c>
+      <c r="C322">
+        <v>80</v>
+      </c>
+      <c r="D322">
+        <v>82</v>
+      </c>
+      <c r="E322">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B323">
+        <v>82</v>
+      </c>
+      <c r="C323">
+        <v>85</v>
+      </c>
+      <c r="D323">
+        <v>93</v>
+      </c>
+      <c r="E323">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B324">
+        <v>60</v>
+      </c>
+      <c r="C324">
+        <v>74</v>
+      </c>
+      <c r="D324">
+        <v>89</v>
+      </c>
+      <c r="E324">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B325">
+        <v>73</v>
+      </c>
+      <c r="C325">
+        <v>86</v>
+      </c>
+      <c r="D325">
+        <v>93</v>
+      </c>
+      <c r="E325">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B326">
+        <v>66</v>
+      </c>
+      <c r="C326">
+        <v>80</v>
+      </c>
+      <c r="D326">
+        <v>85</v>
+      </c>
+      <c r="E326">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B327">
+        <v>59</v>
+      </c>
+      <c r="C327">
+        <v>87</v>
+      </c>
+      <c r="D327">
+        <v>91</v>
+      </c>
+      <c r="E327">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B328">
+        <v>57</v>
+      </c>
+      <c r="C328">
+        <v>81</v>
+      </c>
+      <c r="D328">
+        <v>76</v>
+      </c>
+      <c r="E328">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/情绪指标.xlsx
+++ b/情绪指标.xlsx
@@ -1,28 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="29400" windowHeight="12620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -44,12 +31,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -60,17 +47,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -91,9 +76,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -108,39 +124,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,6 +139,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -170,35 +185,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,109 +200,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -333,7 +224,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,7 +242,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,43 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,6 +391,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -426,7 +422,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -435,22 +431,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -485,11 +466,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,148 +496,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -664,54 +651,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -906,7 +893,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -915,7 +902,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1186,13 +1173,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E328"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
+  <dimension ref="A1:E354"/>
+  <sheetFormatPr defaultColWidth="8.73076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="11.8181818181818"/>
+    <col min="1" max="1" width="11.8173076923077"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="2:5">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -6656,6 +6643,420 @@
       <c r="E328">
         <v>73</v>
       </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B329">
+        <v>69</v>
+      </c>
+      <c r="C329">
+        <v>70</v>
+      </c>
+      <c r="D329">
+        <v>65</v>
+      </c>
+      <c r="E329">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B330">
+        <v>63</v>
+      </c>
+      <c r="C330">
+        <v>71</v>
+      </c>
+      <c r="D330">
+        <v>75</v>
+      </c>
+      <c r="E330">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B331">
+        <v>69</v>
+      </c>
+      <c r="C331">
+        <v>63</v>
+      </c>
+      <c r="D331">
+        <v>59</v>
+      </c>
+      <c r="E331">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B332">
+        <v>77</v>
+      </c>
+      <c r="C332">
+        <v>76</v>
+      </c>
+      <c r="D332">
+        <v>74</v>
+      </c>
+      <c r="E332">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B333">
+        <v>85</v>
+      </c>
+      <c r="C333">
+        <v>75</v>
+      </c>
+      <c r="D333">
+        <v>75</v>
+      </c>
+      <c r="E333">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B334">
+        <v>90</v>
+      </c>
+      <c r="C334">
+        <v>92</v>
+      </c>
+      <c r="D334">
+        <v>93</v>
+      </c>
+      <c r="E334">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B335">
+        <v>88</v>
+      </c>
+      <c r="C335">
+        <v>93</v>
+      </c>
+      <c r="D335">
+        <v>95</v>
+      </c>
+      <c r="E335">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B336">
+        <v>63</v>
+      </c>
+      <c r="C336">
+        <v>78</v>
+      </c>
+      <c r="D336">
+        <v>90</v>
+      </c>
+      <c r="E336">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B337">
+        <v>86</v>
+      </c>
+      <c r="C337">
+        <v>94</v>
+      </c>
+      <c r="D337">
+        <v>95</v>
+      </c>
+      <c r="E337">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B338">
+        <v>79</v>
+      </c>
+      <c r="C338">
+        <v>86</v>
+      </c>
+      <c r="D338">
+        <v>85</v>
+      </c>
+      <c r="E338">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B339">
+        <v>80</v>
+      </c>
+      <c r="C339">
+        <v>92</v>
+      </c>
+      <c r="D339">
+        <v>94</v>
+      </c>
+      <c r="E339">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B340">
+        <v>43</v>
+      </c>
+      <c r="C340">
+        <v>55</v>
+      </c>
+      <c r="D340">
+        <v>62</v>
+      </c>
+      <c r="E340">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B341">
+        <v>33</v>
+      </c>
+      <c r="C341">
+        <v>45</v>
+      </c>
+      <c r="D341">
+        <v>55</v>
+      </c>
+      <c r="E341">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B342">
+        <v>24</v>
+      </c>
+      <c r="C342">
+        <v>39</v>
+      </c>
+      <c r="D342">
+        <v>56</v>
+      </c>
+      <c r="E342">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B343">
+        <v>41</v>
+      </c>
+      <c r="C343">
+        <v>44</v>
+      </c>
+      <c r="D343">
+        <v>63</v>
+      </c>
+      <c r="E343">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B344">
+        <v>40</v>
+      </c>
+      <c r="C344">
+        <v>42</v>
+      </c>
+      <c r="D344">
+        <v>66</v>
+      </c>
+      <c r="E344">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B345">
+        <v>18</v>
+      </c>
+      <c r="C345">
+        <v>25</v>
+      </c>
+      <c r="D345">
+        <v>26</v>
+      </c>
+      <c r="E345">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B346">
+        <v>15</v>
+      </c>
+      <c r="C346">
+        <v>30</v>
+      </c>
+      <c r="D346">
+        <v>45</v>
+      </c>
+      <c r="E346">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B347">
+        <v>42</v>
+      </c>
+      <c r="C347">
+        <v>56</v>
+      </c>
+      <c r="D347">
+        <v>67</v>
+      </c>
+      <c r="E347">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B348">
+        <v>43</v>
+      </c>
+      <c r="C348">
+        <v>58</v>
+      </c>
+      <c r="D348">
+        <v>46</v>
+      </c>
+      <c r="E348">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B349">
+        <v>21</v>
+      </c>
+      <c r="C349">
+        <v>40</v>
+      </c>
+      <c r="D349">
+        <v>24</v>
+      </c>
+      <c r="E349">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B350">
+        <v>14</v>
+      </c>
+      <c r="C350">
+        <v>42</v>
+      </c>
+      <c r="D350">
+        <v>30</v>
+      </c>
+      <c r="E350">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B351">
+        <v>22</v>
+      </c>
+      <c r="C351">
+        <v>35</v>
+      </c>
+      <c r="D351">
+        <v>18</v>
+      </c>
+      <c r="E351">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B352">
+        <v>15</v>
+      </c>
+      <c r="C352">
+        <v>28</v>
+      </c>
+      <c r="D352">
+        <v>14</v>
+      </c>
+      <c r="E352">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="1"/>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
